--- a/stories/arbres/TREE-VIV-019.xlsx
+++ b/stories/arbres/TREE-VIV-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc est au jardin avec papa. Une plante a soif. Papa, l'adulte, prend l'arrosoir. Loïc tient l'anse. Ils versent un peu d'eau. La lumière du soleil arrive. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac, le rebord, ou la serre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1676,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, Loïc verse l'eau avec papa, l'adulte. La lumière chauffe. Eau et lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1857,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Au bac, que fait Loïc ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2030,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc a arrosé. Eau et lumière. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2221,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le basilic, la tomate, ou la fleur.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2388,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc arrose le basilic. Eau. Lumière. Papa, l'adulte, tient l'arrosoir.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2579,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2746,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé le basilic à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2913,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3080,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé le basilic à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3247,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3414,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé le basilic à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3581,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3748,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|La tomate. Loïc verse l'eau. Avec un adulte. La lumière arrive.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3939,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4106,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé la tomate à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4273,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4440,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé la tomate à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4607,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4774,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé la tomate à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4941,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5108,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|La fleur. Loïc arrose. Eau et lumière. Un adulte est là.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5299,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5466,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé la fleur à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5633,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5800,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé la fleur à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5967,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6134,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé la fleur à le bac. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6301,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6468,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Au rebord, Loïc arrose. Papa, l'adulte, guide. Eau. Lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6649,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Au rebord, que fait Loïc ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6822,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On arrose avec un adulte. Eau et lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7013,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le basilic, la tomate, ou la fleur.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7180,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Au rebord, le basilic. Eau. Lumière. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7371,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7538,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé le basilic à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7705,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7872,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé le basilic à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8039,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8206,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé le basilic à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8373,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8540,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|La tomate du rebord. Loïc arrose. Eau. Lumière. Adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8731,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8898,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé la tomate à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9065,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9232,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé la tomate à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9399,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9566,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé la tomate à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9733,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9900,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|La fleur du rebord. Eau et lumière. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10091,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10258,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé la fleur à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10425,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10592,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé la fleur à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10759,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10926,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé la fleur à le rebord. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11093,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10953,6 +11260,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la serre, Loïc verse. Avec un adulte. Eau et lumière.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11441,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la serre, que fait Loïc ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11614,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Loïc a versé l'eau. La lumière est là. Un adulte aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11805,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le basilic, la tomate, ou la fleur.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11972,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Dans la serre, le basilic. Eau. Lumière. Papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12163,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12330,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé le basilic à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12497,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12664,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé le basilic à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12831,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +12998,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé le basilic à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13165,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13332,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|La tomate de la serre. Loïc arrose. Eau. Lumière. Adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13523,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13690,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé la tomate à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13857,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14024,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé la tomate à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14191,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14358,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé la tomate à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14525,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14692,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|La fleur de la serre. Eau et lumière. Avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14883,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15050,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Loïc a arrosé la fleur à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15217,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15384,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|C'est après la sieste. Loïc a arrosé la fleur à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15551,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15718,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Loïc a arrosé la fleur à la serre. Eau et lumière, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15885,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15925,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-VIV-019.xlsx
+++ b/stories/arbres/TREE-VIV-019.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Loïc est au jardin avec papa. Une plante a soif. Papa, l'adulte, prend l'arrosoir. Loïc tient l'anse. Ils versent un peu d'eau. La lumière du soleil arrive. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac, le rebord, ou la serre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1681,6 +1688,7 @@
           <t>narrateur|Au bac, Loïc verse l'eau avec papa, l'adulte. La lumière chauffe. Eau et lumière.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1864,6 +1872,7 @@
           <t>narrateur|Au bac, que fait Loïc ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2035,6 +2044,7 @@
           <t>narrateur|Loïc a arrosé. Eau et lumière. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2226,6 +2236,7 @@
           <t>narrateur|On peut prendre le basilic, la tomate, ou la fleur.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2393,6 +2404,7 @@
           <t>narrateur|Loïc arrose le basilic. Eau. Lumière. Papa, l'adulte, tient l'arrosoir.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2584,6 +2596,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2751,6 +2764,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé le basilic à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2918,6 +2932,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3085,6 +3100,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé le basilic à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3252,6 +3268,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3419,6 +3436,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé le basilic à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3586,6 +3604,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3753,6 +3772,7 @@
           <t>narrateur|La tomate. Loïc verse l'eau. Avec un adulte. La lumière arrive.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3944,6 +3964,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4111,6 +4132,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé la tomate à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4278,6 +4300,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4445,6 +4468,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé la tomate à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4612,6 +4636,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4779,6 +4804,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé la tomate à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4946,6 +4972,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5113,6 +5140,7 @@
           <t>narrateur|La fleur. Loïc arrose. Eau et lumière. Un adulte est là.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5304,6 +5332,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5471,6 +5500,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé la fleur à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5638,6 +5668,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5805,6 +5836,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé la fleur à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5972,6 +6004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6139,6 +6172,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé la fleur à le bac. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6306,6 +6340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6473,6 +6508,7 @@
           <t>narrateur|Au rebord, Loïc arrose. Papa, l'adulte, guide. Eau. Lumière.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6656,6 +6692,7 @@
           <t>narrateur|Au rebord, que fait Loïc ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6827,6 +6864,7 @@
           <t>narrateur|Oui. On arrose avec un adulte. Eau et lumière.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7018,6 +7056,7 @@
           <t>narrateur|On peut prendre le basilic, la tomate, ou la fleur.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7185,6 +7224,7 @@
           <t>narrateur|Au rebord, le basilic. Eau. Lumière. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7376,6 +7416,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7543,6 +7584,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé le basilic à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7710,6 +7752,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7877,6 +7920,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé le basilic à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8044,6 +8088,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8211,6 +8256,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé le basilic à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8378,6 +8424,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8545,6 +8592,7 @@
           <t>narrateur|La tomate du rebord. Loïc arrose. Eau. Lumière. Adulte.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8736,6 +8784,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8903,6 +8952,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé la tomate à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9070,6 +9120,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9237,6 +9288,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé la tomate à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9404,6 +9456,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9571,6 +9624,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé la tomate à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9738,6 +9792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9905,6 +9960,7 @@
           <t>narrateur|La fleur du rebord. Eau et lumière. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10096,6 +10152,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10263,6 +10320,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé la fleur à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10430,6 +10488,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10597,6 +10656,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé la fleur à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10764,6 +10824,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10931,6 +10992,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé la fleur à le rebord. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11098,6 +11160,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11265,6 +11328,7 @@
           <t>narrateur|Dans la serre, Loïc verse. Avec un adulte. Eau et lumière.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11448,6 +11512,7 @@
           <t>narrateur|Dans la serre, que fait Loïc ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11619,6 +11684,7 @@
           <t>narrateur|Loïc a versé l'eau. La lumière est là. Un adulte aussi.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11810,6 +11876,7 @@
           <t>narrateur|On peut prendre le basilic, la tomate, ou la fleur.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11977,6 +12044,7 @@
           <t>narrateur|Dans la serre, le basilic. Eau. Lumière. Papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12168,6 +12236,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12335,6 +12404,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé le basilic à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12502,6 +12572,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12669,6 +12740,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé le basilic à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12836,6 +12908,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13003,6 +13076,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé le basilic à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13170,6 +13244,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13337,6 +13412,7 @@
           <t>narrateur|La tomate de la serre. Loïc arrose. Eau. Lumière. Adulte.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13528,6 +13604,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13695,6 +13772,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé la tomate à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13862,6 +13940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14029,6 +14108,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé la tomate à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14196,6 +14276,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14363,6 +14444,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé la tomate à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14530,6 +14612,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14697,6 +14780,7 @@
           <t>narrateur|La fleur de la serre. Eau et lumière. Avec un adulte.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14888,6 +14972,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15055,6 +15140,7 @@
           <t>narrateur|C'est le matin. Loïc a arrosé la fleur à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15222,6 +15308,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15389,6 +15476,7 @@
           <t>narrateur|C'est après la sieste. Loïc a arrosé la fleur à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15556,6 +15644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15723,6 +15812,7 @@
           <t>narrateur|C'est le soir. Loïc a arrosé la fleur à la serre. Eau et lumière, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15890,6 +15980,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15908,7 +15999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15932,6 +16023,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15946,7 +16051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16133,6 +16238,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
